--- a/documentation/data_architecture.xlsx
+++ b/documentation/data_architecture.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jadul\desktop_data_engineering\Banking_Risk_Operations_Dashboard\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A4EC72-1A9D-4F8B-A492-170DC56A36DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E93A8F-A43B-437E-B675-8928E6DC0923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="726" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="174">
   <si>
     <t>Requirement</t>
   </si>
@@ -400,12 +400,6 @@
     <t>dim_time</t>
   </si>
   <si>
-    <t>dim_transaction_type</t>
-  </si>
-  <si>
-    <t>Describes the transaction category</t>
-  </si>
-  <si>
     <t>nameOrig</t>
   </si>
   <si>
@@ -454,12 +448,6 @@
     <t>Stores the simulation-step information</t>
   </si>
   <si>
-    <t>Stores the transaction type categories</t>
-  </si>
-  <si>
-    <t>fact_transaction table</t>
-  </si>
-  <si>
     <t>Column</t>
   </si>
   <si>
@@ -485,22 +473,6 @@
     </r>
   </si>
   <si>
-    <t>transaction_type_key</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Reference to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>dim_transaction_type</t>
-    </r>
-  </si>
-  <si>
     <t>amount</t>
   </si>
   <si>
@@ -567,12 +539,6 @@
     <t>dim_time table</t>
   </si>
   <si>
-    <t>TRANSFER</t>
-  </si>
-  <si>
-    <t>dim_transaction_type table</t>
-  </si>
-  <si>
     <t>25 (25th simulated hour)</t>
   </si>
   <si>
@@ -580,30 +546,6 @@
   </si>
   <si>
     <t>1 (hour 1 of day 2)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Physical Model Summary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:
-The physical model translated the logical model into a practical database structure based on the fields actually available in the PaySim dataset. A fact_transaction table stores transaction-level data, while dim_time organizes the simulation step into day and hour attributes, and dim_transaction_type standardizes transaction categories.</t>
-    </r>
   </si>
   <si>
     <t>Data Architecture Flow</t>
@@ -899,6 +841,39 @@
   </si>
   <si>
     <t>isFraud = 1, isFlaggedFraud = 0</t>
+  </si>
+  <si>
+    <t>fact_transactions table</t>
+  </si>
+  <si>
+    <t>fact_transactions</t>
+  </si>
+  <si>
+    <t>Transaction type</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Physical Model Summary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:
+The physical model translated the logical model into a practical database structure based on the fields actually available in the PaySim dataset. A fact_transaction table stores transaction-level data, while dim_time organizes the simulation step into day and hour attributes.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -968,7 +943,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -993,8 +968,14 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1042,26 +1023,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </left>
@@ -1079,7 +1040,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1115,7 +1076,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1124,33 +1085,28 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="33">
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1159,182 +1115,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Unicode MS"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Unicode MS"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Unicode MS"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Unicode MS"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1536,6 +1316,132 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Unicode MS"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2637,7 +2543,7 @@
           </a:pPr>
           <a:r>
             <a:rPr lang="en-PH" sz="1000" baseline="0"/>
-            <a:t>fact_transaction, dim_tables</a:t>
+            <a:t>fact_transaction, dim_table</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3146,143 +3052,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>96992</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>126720</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="Freeform: Shape 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56C055BC-C911-7801-6F42-A6ED64E83959}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6619875" y="1811492"/>
-          <a:ext cx="1057275" cy="1363228"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst>
-            <a:gd name="csX0" fmla="*/ 0 w 990600"/>
-            <a:gd name="csY0" fmla="*/ 69191 h 1249148"/>
-            <a:gd name="csX1" fmla="*/ 457200 w 990600"/>
-            <a:gd name="csY1" fmla="*/ 116816 h 1249148"/>
-            <a:gd name="csX2" fmla="*/ 619125 w 990600"/>
-            <a:gd name="csY2" fmla="*/ 1155041 h 1249148"/>
-            <a:gd name="csX3" fmla="*/ 990600 w 990600"/>
-            <a:gd name="csY3" fmla="*/ 1193141 h 1249148"/>
-            <a:gd name="csX0" fmla="*/ 0 w 990600"/>
-            <a:gd name="csY0" fmla="*/ 28990 h 1200858"/>
-            <a:gd name="csX1" fmla="*/ 494937 w 990600"/>
-            <a:gd name="csY1" fmla="*/ 189529 h 1200858"/>
-            <a:gd name="csX2" fmla="*/ 619125 w 990600"/>
-            <a:gd name="csY2" fmla="*/ 1114840 h 1200858"/>
-            <a:gd name="csX3" fmla="*/ 990600 w 990600"/>
-            <a:gd name="csY3" fmla="*/ 1152940 h 1200858"/>
-            <a:gd name="csX0" fmla="*/ 0 w 990600"/>
-            <a:gd name="csY0" fmla="*/ 27369 h 1169047"/>
-            <a:gd name="csX1" fmla="*/ 494937 w 990600"/>
-            <a:gd name="csY1" fmla="*/ 187908 h 1169047"/>
-            <a:gd name="csX2" fmla="*/ 565579 w 990600"/>
-            <a:gd name="csY2" fmla="*/ 1056041 h 1169047"/>
-            <a:gd name="csX3" fmla="*/ 990600 w 990600"/>
-            <a:gd name="csY3" fmla="*/ 1151319 h 1169047"/>
-          </a:gdLst>
-          <a:ahLst/>
-          <a:cxnLst>
-            <a:cxn ang="0">
-              <a:pos x="csX0" y="csY0"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="csX1" y="csY1"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="csX2" y="csY2"/>
-            </a:cxn>
-            <a:cxn ang="0">
-              <a:pos x="csX3" y="csY3"/>
-            </a:cxn>
-          </a:cxnLst>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="990600" h="1169047">
-              <a:moveTo>
-                <a:pt x="0" y="27369"/>
-              </a:moveTo>
-              <a:cubicBezTo>
-                <a:pt x="177006" y="-39306"/>
-                <a:pt x="400674" y="16463"/>
-                <a:pt x="494937" y="187908"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="589200" y="359353"/>
-                <a:pt x="482969" y="895473"/>
-                <a:pt x="565579" y="1056041"/>
-              </a:cubicBezTo>
-              <a:cubicBezTo>
-                <a:pt x="648189" y="1216609"/>
-                <a:pt x="882650" y="1162432"/>
-                <a:pt x="990600" y="1151319"/>
-              </a:cubicBezTo>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="40000"/>
-            </a:prstClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-PH" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -3350,71 +3119,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>457065</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>76140</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>457425</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>8760</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
-      <mc:Choice Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="64" name="Ink 63">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27F84E07-F785-CF63-D101-6E6F63EEA491}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="7572240" y="3124140"/>
-            <a:ext cx="360" cy="123120"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="64" name="Ink 63">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27F84E07-F785-CF63-D101-6E6F63EEA491}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7566120" y="3118020"/>
-              <a:ext cx="12600" cy="135360"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>67916</xdr:colOff>
       <xdr:row>8</xdr:row>
@@ -3428,7 +3132,7 @@
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
       <mc:Choice Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="82" name="Ink 81">
               <a:extLst>
@@ -3543,71 +3247,6 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>62156</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>50421</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>143876</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>158421</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
-      <mc:Choice Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="90" name="Ink 89">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{969A6274-75EA-B0E8-2F22-84A17E22AB82}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="6567731" y="1764921"/>
-            <a:ext cx="81720" cy="108000"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="90" name="Ink 89">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{969A6274-75EA-B0E8-2F22-84A17E22AB82}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6561611" y="1758801"/>
-              <a:ext cx="93960" cy="120240"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3654,33 +3293,6 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-08-08T07:35:08.343"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.035" units="cm"/>
-      <inkml:brushProperty name="height" value="0.035" units="cm"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 0 24575,'0'5'0,"0"5"0,0 6 0,0 5 0,0 3 0,0 2 0,0 1 0,0 1 0,0 0 0,0-1 0,0 0 0,0 0 0,0 0 0,0-1 0,0-4-8191</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
       <inkml:timestamp xml:id="ts0" timeString="2026-08-08T07:35:52.531"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
@@ -3693,7 +3305,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink3.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -3721,56 +3333,17 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink5.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-08-08T07:36:07.272"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.035" units="cm"/>
-      <inkml:brushProperty name="height" value="0.035" units="cm"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">181 229 24575,'0'2'0,"-4"1"0,-1 1 0,-2 1 0,-2-2 0,0 2 0,-2 2 0,0-1 0,-1-1 0,0-2 0,3 1 0,-1 0 0,1-1 0,0-1 0,1 1 0,0 0 0,-1 2 0,2-1-8191</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="2156.11">204 183 24575,'-26'-1'43,"1"-1"0,-26-7-1,-41-2-1535,82 11-5333</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="3921.6">227 195 24575,'-28'-31'0,"1"-2"0,-33-52 0,37 47-1365,18 31-5461</inkml:trace>
-</inkml:ink>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3169706F-B0BA-41D0-A9B7-2B8EB148B2CF}" name="Table14" displayName="Table14" ref="A18:B26" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3169706F-B0BA-41D0-A9B7-2B8EB148B2CF}" name="Table14" displayName="Table14" ref="A18:B26" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A6084305-3ADF-4002-9244-B22BC2B24989}" name="Area" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{03082AB2-2A4A-46C3-93B7-18281C809A2D}" name="Decision" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{A6084305-3ADF-4002-9244-B22BC2B24989}" name="Area" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{03082AB2-2A4A-46C3-93B7-18281C809A2D}" name="Decision" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{279F989E-7B81-4084-92FB-A99D5253D1D2}" name="Table11" displayName="Table11" ref="A1:B7" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5B0952E7-B206-4119-AC09-8E30C7604DF2}" name="Item" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{D3AC1F06-0A41-408C-B8F4-AF2F632AD94D}" name="Decision" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{DA73E088-707D-4FE1-8ADE-9B19F26D92EC}" name="Table6" displayName="Table6" ref="A1:B7" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{A11218D2-A7C7-42C1-B4DD-E669863D45F7}" name="Item"/>
@@ -3781,11 +3354,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{119629F7-F6D2-4CA2-9C4A-2B234E48A5C8}" name="Table1" displayName="Table1" ref="A1:C10" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{119629F7-F6D2-4CA2-9C4A-2B234E48A5C8}" name="Table1" displayName="Table1" ref="A1:C10" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0835AB9E-4496-49BB-88EC-897CED691C28}" name="Requirement" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{0E4906C3-F274-441A-9BB7-3F309546C659}" name="Business Reason" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{D37467CF-9FAE-40AB-8FF1-A205F393AD6C}" name="Engineering Reason" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{0835AB9E-4496-49BB-88EC-897CED691C28}" name="Requirement" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{0E4906C3-F274-441A-9BB7-3F309546C659}" name="Business Reason" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{D37467CF-9FAE-40AB-8FF1-A205F393AD6C}" name="Engineering Reason" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3804,65 +3377,64 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4E1A9F7C-15F0-45CE-9693-3F6034E0AFD5}" name="Table5" displayName="Table5" ref="A1:C6" totalsRowShown="0" headerRowDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4E1A9F7C-15F0-45CE-9693-3F6034E0AFD5}" name="Table5" displayName="Table5" ref="A1:C6" totalsRowShown="0" headerRowDxfId="12">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0FB6EA6A-4B29-4AA4-8631-9C112AE45F44}" name="Entity" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{5FBFCC0A-142C-4802-B330-C7CD4BEF4EE7}" name="Purpose" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{8C7EA281-882B-42AE-9F0E-9FDE81C9DD0F}" name="Source Columns" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{0FB6EA6A-4B29-4AA4-8631-9C112AE45F44}" name="Entity" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{5FBFCC0A-142C-4802-B330-C7CD4BEF4EE7}" name="Purpose" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{8C7EA281-882B-42AE-9F0E-9FDE81C9DD0F}" name="Source Columns" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{88AD8F42-CA88-4880-88D4-E007930FB1F0}" name="Table8" displayName="Table8" ref="A1:C4" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{88AD8F42-CA88-4880-88D4-E007930FB1F0}" name="Table8" displayName="Table8" ref="A1:C3" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0680D262-2BCE-4C60-971F-8F40E4F42D49}" name="Component" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{B245B01B-0D52-43C9-97E1-112C5937A59B}" name="Purpose" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{5A2DDD02-0DBA-456F-9E39-92F3E938AD5C}" name="Source Columns" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{0680D262-2BCE-4C60-971F-8F40E4F42D49}" name="Component" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{B245B01B-0D52-43C9-97E1-112C5937A59B}" name="Purpose" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{5A2DDD02-0DBA-456F-9E39-92F3E938AD5C}" name="Source Columns" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{72A96B09-4F6C-4CDF-AD94-DDD7EDC3DB49}" name="Table9" displayName="Table9" ref="A1:B4" totalsRowShown="0" headerRowDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{72A96B09-4F6C-4CDF-AD94-DDD7EDC3DB49}" name="Table9" displayName="Table9" ref="A1:B4" totalsRowShown="0" headerRowDxfId="32">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{F79C8D97-4658-4710-AA07-7B42934ED0AF}" name="Table" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{FC0B3307-A070-48DA-82A6-5C153BEA6CEE}" name="Purpose" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{F79C8D97-4658-4710-AA07-7B42934ED0AF}" name="Table" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{FC0B3307-A070-48DA-82A6-5C153BEA6CEE}" name="Purpose" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6E51C46D-E79D-4D86-98CA-3ED4D3A87832}" name="Table10" displayName="Table10" ref="A8:C22" totalsRowShown="0" headerRowDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{6E51C46D-E79D-4D86-98CA-3ED4D3A87832}" name="Table10" displayName="Table10" ref="A8:C22" totalsRowShown="0" headerRowDxfId="29">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{793B99E3-83A8-4876-903B-C20760596E9B}" name="Column" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{7EDE9CA5-5E84-4B80-87F3-77971ED280F5}" name="Type" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{F0EBFA39-2B75-4D05-B77C-D7628E802CF9}" name="Role" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{793B99E3-83A8-4876-903B-C20760596E9B}" name="Column" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{7EDE9CA5-5E84-4B80-87F3-77971ED280F5}" name="Type" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{F0EBFA39-2B75-4D05-B77C-D7628E802CF9}" name="Role" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{7A0C4740-D249-4893-BDEE-106421B2699B}" name="Table12" displayName="Table12" ref="F8:H12" totalsRowShown="0" headerRowDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{7A0C4740-D249-4893-BDEE-106421B2699B}" name="Table12" displayName="Table12" ref="F8:H12" totalsRowShown="0" headerRowDxfId="25">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{F75D3A09-2A9F-478E-9163-61829F575BF9}" name="Column" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{5EB27C13-129A-4E62-9D3F-44419156B4D7}" name="Type" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{A35C2ACC-F573-4767-9D3F-DF3C99189C53}" name="Sample" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{F75D3A09-2A9F-478E-9163-61829F575BF9}" name="Column" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{5EB27C13-129A-4E62-9D3F-44419156B4D7}" name="Type" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{A35C2ACC-F573-4767-9D3F-DF3C99189C53}" name="Sample" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{98511C7E-975F-4207-8331-AA927BFE2CCF}" name="Table13" displayName="Table13" ref="F16:H18" totalsRowShown="0" headerRowDxfId="8" tableBorderDxfId="7">
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2B8AAD8C-58E9-4496-BB60-65F519861419}" name="Column" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{BA554336-825A-493D-A5A4-C3293AB7B09B}" name="Type" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{B6EB9CB4-5339-42E8-9DC0-D6602ABFF931}" name="Sample" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{279F989E-7B81-4084-92FB-A99D5253D1D2}" name="Table11" displayName="Table11" ref="A1:B7" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{5B0952E7-B206-4119-AC09-8E30C7604DF2}" name="Item" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{D3AC1F06-0A41-408C-B8F4-AF2F632AD94D}" name="Decision" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4141,125 +3713,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
-      <c r="A1" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="A1" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C18" s="11"/>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C19" s="11"/>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C20" s="11"/>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C21" s="11"/>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C22" s="11"/>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1">
-      <c r="A29" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="B29" s="17"/>
+      <c r="A29" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29" s="18"/>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
     </row>
     <row r="33" spans="1:2" ht="15" customHeight="1">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4396,7 +3968,7 @@
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1">
       <c r="A13" s="13" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1">
@@ -4407,7 +3979,7 @@
         <v>31</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1">
@@ -4418,7 +3990,7 @@
         <v>33</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="3:3" ht="15" customHeight="1">
@@ -4468,7 +4040,7 @@
         <v>37</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1">
@@ -4476,10 +4048,10 @@
         <v>42</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1">
@@ -4487,10 +4059,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1">
@@ -4498,10 +4070,10 @@
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1">
@@ -4509,10 +4081,10 @@
         <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
@@ -4520,10 +4092,10 @@
         <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
@@ -4534,7 +4106,7 @@
         <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -4622,34 +4194,34 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="17"/>
+      <c r="B8" s="18"/>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4664,7 +4236,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C442377-6B16-4FED-B91F-E197BEFA5084}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
@@ -4685,13 +4257,13 @@
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1">
@@ -4699,68 +4271,57 @@
         <v>64</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1">
-      <c r="A4" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>58</v>
-      </c>
+    <row r="6" spans="1:3" ht="15" customHeight="1">
+      <c r="A6" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="18"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1">
       <c r="A15" s="11"/>
       <c r="B15" s="11"/>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:B14"/>
+    <mergeCell ref="A6:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -4784,92 +4345,88 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="D1" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+        <v>72</v>
+      </c>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1">
       <c r="A3" s="12" t="s">
         <v>64</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
+        <v>73</v>
+      </c>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
-      <c r="A4" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
-      <c r="A7" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="19"/>
-      <c r="F7" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="G7" s="18"/>
-      <c r="H7" s="19"/>
+      <c r="A7" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="F7" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>41</v>
@@ -4880,237 +4437,203 @@
         <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>61</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>84</v>
+        <v>172</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" s="20"/>
-      <c r="H15" s="21"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
       <c r="A16" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" customHeight="1">
+      <c r="A17" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" customHeight="1">
+      <c r="A18" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" s="2" t="s">
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1">
+      <c r="A19" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1">
-      <c r="A17" s="12" t="s">
+      <c r="B19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H17" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1">
-      <c r="A18" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1">
-      <c r="A19" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1">
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F15:H15"/>
     <mergeCell ref="D1:H5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <tableParts count="4">
+  <tableParts count="3">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
-    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5129,39 +4652,39 @@
         <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1">
@@ -5169,34 +4692,34 @@
         <v>47</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" customHeight="1">
-      <c r="A10" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="17"/>
+      <c r="A10" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="18"/>
     </row>
     <row r="11" spans="1:2" ht="15" customHeight="1">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5226,148 +4749,148 @@
         <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" customHeight="1">
-      <c r="A10" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B10" s="17"/>
+      <c r="A10" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="18"/>
     </row>
     <row r="11" spans="1:2" ht="15" customHeight="1">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
     </row>
     <row r="16" spans="1:2" ht="15" customHeight="1">
-      <c r="A16" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="B16" s="22"/>
+      <c r="A16" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="20"/>
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
     </row>
     <row r="19" spans="1:2" ht="15" customHeight="1">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
     </row>
     <row r="20" spans="1:2" ht="15" customHeight="1">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
     </row>
     <row r="21" spans="1:2" ht="15" customHeight="1">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
     </row>
     <row r="22" spans="1:2" ht="15" customHeight="1">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
     </row>
     <row r="23" spans="1:2" ht="15" customHeight="1">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
     </row>
     <row r="24" spans="1:2" ht="15" customHeight="1">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
     </row>
     <row r="25" spans="1:2" ht="15" customHeight="1">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
     </row>
     <row r="26" spans="1:2" ht="15" customHeight="1">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
     </row>
     <row r="27" spans="1:2" ht="15" customHeight="1">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
     </row>
     <row r="28" spans="1:2" ht="15" customHeight="1">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
     </row>
     <row r="29" spans="1:2" ht="15" customHeight="1">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
     </row>
     <row r="30" spans="1:2" ht="15" customHeight="1">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
     </row>
     <row r="31" spans="1:2" ht="15" customHeight="1">
-      <c r="A31" s="22"/>
-      <c r="B31" s="22"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
     </row>
     <row r="32" spans="1:2" ht="15" customHeight="1">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
     </row>
     <row r="33" spans="1:2" ht="15" customHeight="1">
       <c r="A33" s="11"/>
